--- a/剧情文件及美术补充/静语纹_四章剧情_无旁白版_v2.xlsx
+++ b/剧情文件及美术补充/静语纹_四章剧情_无旁白版_v2.xlsx
@@ -364,7 +364,7 @@
     <t>他们管这叫“经验现象”。没有学院的人署名，就进不了正式档案。别皱眉，我都抱怨好多年了。</t>
   </si>
   <si>
-    <t>1-3</t>
+    <t>1-4</t>
   </si>
   <si>
     <t>伦敦街上</t>
@@ -388,7 +388,7 @@
     <t>因为外形只是载体。真正统一它们的是学院给出的程式。工坊的任务，是把程式可靠地实现出来。</t>
   </si>
   <si>
-    <t>1-4</t>
+    <t>1-5</t>
   </si>
   <si>
     <t>威客利夫先生走得真急……等等，检验台下面这本黑色笔记，是他的吧？</t>
